--- a/Windows/LivreNoirLibrary.Windows.Media.Integrated/Themes/BmsSkin/skin_memo.xlsx
+++ b/Windows/LivreNoirLibrary.Windows.Media.Integrated/Themes/BmsSkin/skin_memo.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualStudio\LivreNoirLibrary10\Windows\LivreNoirLibrary.Windows.Media.Integrated\Themes\BmsSkin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029C60A7-2B17-4D2A-8012-8DBB31C11578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D8BE7F-4A14-425F-A1BC-03C885ABBC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23940" yWindow="810" windowWidth="22845" windowHeight="14460" xr2:uid="{C33A0C8D-C268-4B2F-941E-C4C9B83FD88F}"/>
+    <workbookView xWindow="-23520" yWindow="1275" windowWidth="22845" windowHeight="14235" activeTab="1" xr2:uid="{C33A0C8D-C268-4B2F-941E-C4C9B83FD88F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="beam" sheetId="1" r:id="rId1"/>
+    <sheet name="timerId" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="27">
   <si>
     <t>x</t>
     <phoneticPr fontId="1"/>
@@ -95,6 +96,38 @@
   <si>
     <t>&lt;Destination Time="0.12" Height="$Options.Beam Height"/&gt;&lt;/Image&gt;</t>
   </si>
+  <si>
+    <t>Press</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Release</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bomb</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LongBomb</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mine</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Judge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Early</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Late</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -139,11 +172,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -519,7 +549,7 @@
         <f>"&lt;Destination Rect="""&amp;C2&amp;", 512, "&amp;B2&amp;", 0"" Origin=""0.5, 1""/&gt;"</f>
         <v>&lt;Destination Rect="32, 512, 60, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>10</v>
       </c>
       <c r="J2" t="str">
@@ -563,7 +593,7 @@
         <f t="shared" ref="H3:H9" si="2">"&lt;Destination Rect="""&amp;C3&amp;", 512, "&amp;B3&amp;", 0"" Origin=""0.5, 1""/&gt;"</f>
         <v>&lt;Destination Rect="83, 512, 38, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>12</v>
       </c>
       <c r="J3" t="str">
@@ -607,7 +637,7 @@
         <f t="shared" si="2"/>
         <v>&lt;Destination Rect="119, 512, 30, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>13</v>
       </c>
       <c r="J4" t="str">
@@ -651,7 +681,7 @@
         <f t="shared" si="2"/>
         <v>&lt;Destination Rect="155, 512, 38, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="str">
@@ -695,7 +725,7 @@
         <f t="shared" si="2"/>
         <v>&lt;Destination Rect="191, 512, 30, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>15</v>
       </c>
       <c r="J6" t="str">
@@ -739,7 +769,7 @@
         <f t="shared" si="2"/>
         <v>&lt;Destination Rect="227, 512, 38, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>16</v>
       </c>
       <c r="J7" t="str">
@@ -783,7 +813,7 @@
         <f t="shared" si="2"/>
         <v>&lt;Destination Rect="263, 512, 30, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>17</v>
       </c>
       <c r="J8" t="str">
@@ -827,7 +857,7 @@
         <f t="shared" si="2"/>
         <v>&lt;Destination Rect="299, 512, 38, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>18</v>
       </c>
       <c r="J9" t="str">
@@ -870,7 +900,7 @@
         <f>"&lt;Destination Rect="""&amp;C11&amp;", 512, "&amp;B11&amp;", 0"" Origin=""0.5, 1""/&gt;"</f>
         <v>&lt;Destination Rect="21, 512, 38, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" t="str">
@@ -914,7 +944,7 @@
         <f t="shared" ref="H12:H18" si="8">"&lt;Destination Rect="""&amp;C12&amp;", 512, "&amp;B12&amp;", 0"" Origin=""0.5, 1""/&gt;"</f>
         <v>&lt;Destination Rect="57, 512, 30, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>12</v>
       </c>
       <c r="J12" t="str">
@@ -958,7 +988,7 @@
         <f t="shared" si="8"/>
         <v>&lt;Destination Rect="93, 512, 38, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>13</v>
       </c>
       <c r="J13" t="str">
@@ -1002,7 +1032,7 @@
         <f t="shared" si="8"/>
         <v>&lt;Destination Rect="129, 512, 30, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>14</v>
       </c>
       <c r="J14" t="str">
@@ -1046,7 +1076,7 @@
         <f t="shared" si="8"/>
         <v>&lt;Destination Rect="165, 512, 38, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>15</v>
       </c>
       <c r="J15" t="str">
@@ -1090,7 +1120,7 @@
         <f t="shared" si="8"/>
         <v>&lt;Destination Rect="201, 512, 30, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" t="s">
         <v>16</v>
       </c>
       <c r="J16" t="str">
@@ -1134,7 +1164,7 @@
         <f t="shared" si="8"/>
         <v>&lt;Destination Rect="237, 512, 38, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" t="s">
         <v>17</v>
       </c>
       <c r="J17" t="str">
@@ -1178,7 +1208,7 @@
         <f t="shared" si="8"/>
         <v>&lt;Destination Rect="288, 512, 60, 0" Origin="0.5, 1"/&gt;</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>18</v>
       </c>
       <c r="J18" t="str">
@@ -1191,6 +1221,5321 @@
       </c>
       <c r="L18" t="s">
         <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E07D7-A47F-40A1-AAE7-F9281CAEE926}">
+  <dimension ref="A2:G426"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="84.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="str">
+        <f>IF(A2="","","        Play_Button"&amp;A2&amp;"_"&amp;B2&amp;" = TimerIdOffsets.Button + "&amp;A2&amp;"0 + TimerIdOffsets."&amp;B2&amp;",")</f>
+        <v xml:space="preserve">        Play_Button1_Press = TimerIdOffsets.Button + 10 + TimerIdOffsets.Press,</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="str">
+        <f>IF(E2="","","        Play_"&amp;E2&amp;"P_"&amp;F2&amp;" = TimerIdOffsets.PlayerJudge + "&amp;E2&amp;"0 + TimerIdOffsets."&amp;F2&amp;",")</f>
+        <v xml:space="preserve">        Play_1P_Judge = TimerIdOffsets.PlayerJudge + 10 + TimerIdOffsets.Judge,</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C66" si="0">IF(A3="","","        Play_Button"&amp;A3&amp;"_"&amp;B3&amp;" = TimerIdOffsets.Button + "&amp;A3&amp;"0 + TimerIdOffsets."&amp;B3&amp;",")</f>
+        <v xml:space="preserve">        Play_Button1_Release = TimerIdOffsets.Button + 10 + TimerIdOffsets.Release,</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G32" si="1">IF(E3="","","        Play_"&amp;E3&amp;"P_"&amp;F3&amp;" = TimerIdOffsets.PlayerJudge + "&amp;E3&amp;"0 + TimerIdOffsets."&amp;F3&amp;",")</f>
+        <v xml:space="preserve">        Play_1P_Early = TimerIdOffsets.PlayerJudge + 10 + TimerIdOffsets.Early,</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button1_Bomb = TimerIdOffsets.Button + 10 + TimerIdOffsets.Bomb,</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_1P_Late = TimerIdOffsets.PlayerJudge + 10 + TimerIdOffsets.Late,</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button1_LongBomb = TimerIdOffsets.Button + 10 + TimerIdOffsets.LongBomb,</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button1_Mine = TimerIdOffsets.Button + 10 + TimerIdOffsets.Mine,</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_2P_Judge = TimerIdOffsets.PlayerJudge + 20 + TimerIdOffsets.Judge,</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_2P_Early = TimerIdOffsets.PlayerJudge + 20 + TimerIdOffsets.Early,</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button2_Press = TimerIdOffsets.Button + 20 + TimerIdOffsets.Press,</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_2P_Late = TimerIdOffsets.PlayerJudge + 20 + TimerIdOffsets.Late,</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <f t="shared" ref="A9:A12" si="2">A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button2_Release = TimerIdOffsets.Button + 20 + TimerIdOffsets.Release,</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button2_Bomb = TimerIdOffsets.Button + 20 + TimerIdOffsets.Bomb,</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_3P_Judge = TimerIdOffsets.PlayerJudge + 30 + TimerIdOffsets.Judge,</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button2_LongBomb = TimerIdOffsets.Button + 20 + TimerIdOffsets.LongBomb,</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_3P_Early = TimerIdOffsets.PlayerJudge + 30 + TimerIdOffsets.Early,</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button2_Mine = TimerIdOffsets.Button + 20 + TimerIdOffsets.Mine,</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_3P_Late = TimerIdOffsets.PlayerJudge + 30 + TimerIdOffsets.Late,</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <f t="shared" ref="A14:A77" si="3">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button3_Press = TimerIdOffsets.Button + 30 + TimerIdOffsets.Press,</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_4P_Judge = TimerIdOffsets.PlayerJudge + 40 + TimerIdOffsets.Judge,</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button3_Release = TimerIdOffsets.Button + 30 + TimerIdOffsets.Release,</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_4P_Early = TimerIdOffsets.PlayerJudge + 40 + TimerIdOffsets.Early,</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button3_Bomb = TimerIdOffsets.Button + 30 + TimerIdOffsets.Bomb,</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_4P_Late = TimerIdOffsets.PlayerJudge + 40 + TimerIdOffsets.Late,</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button3_LongBomb = TimerIdOffsets.Button + 30 + TimerIdOffsets.LongBomb,</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button3_Mine = TimerIdOffsets.Button + 30 + TimerIdOffsets.Mine,</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_5P_Judge = TimerIdOffsets.PlayerJudge + 50 + TimerIdOffsets.Judge,</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_5P_Early = TimerIdOffsets.PlayerJudge + 50 + TimerIdOffsets.Early,</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <f t="shared" ref="A20" si="4">A14+1</f>
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button4_Press = TimerIdOffsets.Button + 40 + TimerIdOffsets.Press,</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_5P_Late = TimerIdOffsets.PlayerJudge + 50 + TimerIdOffsets.Late,</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button4_Release = TimerIdOffsets.Button + 40 + TimerIdOffsets.Release,</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button4_Bomb = TimerIdOffsets.Button + 40 + TimerIdOffsets.Bomb,</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_6P_Judge = TimerIdOffsets.PlayerJudge + 60 + TimerIdOffsets.Judge,</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button4_LongBomb = TimerIdOffsets.Button + 40 + TimerIdOffsets.LongBomb,</v>
+      </c>
+      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_6P_Early = TimerIdOffsets.PlayerJudge + 60 + TimerIdOffsets.Early,</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button4_Mine = TimerIdOffsets.Button + 40 + TimerIdOffsets.Mine,</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_6P_Late = TimerIdOffsets.PlayerJudge + 60 + TimerIdOffsets.Late,</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <f t="shared" ref="A26" si="5">A20+1</f>
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button5_Press = TimerIdOffsets.Button + 50 + TimerIdOffsets.Press,</v>
+      </c>
+      <c r="E26">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_7P_Judge = TimerIdOffsets.PlayerJudge + 70 + TimerIdOffsets.Judge,</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button5_Release = TimerIdOffsets.Button + 50 + TimerIdOffsets.Release,</v>
+      </c>
+      <c r="E27">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_7P_Early = TimerIdOffsets.PlayerJudge + 70 + TimerIdOffsets.Early,</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button5_Bomb = TimerIdOffsets.Button + 50 + TimerIdOffsets.Bomb,</v>
+      </c>
+      <c r="E28">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_7P_Late = TimerIdOffsets.PlayerJudge + 70 + TimerIdOffsets.Late,</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button5_LongBomb = TimerIdOffsets.Button + 50 + TimerIdOffsets.LongBomb,</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button5_Mine = TimerIdOffsets.Button + 50 + TimerIdOffsets.Mine,</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_8P_Judge = TimerIdOffsets.PlayerJudge + 80 + TimerIdOffsets.Judge,</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E31">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_8P_Early = TimerIdOffsets.PlayerJudge + 80 + TimerIdOffsets.Early,</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <f t="shared" ref="A32" si="6">A26+1</f>
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button6_Press = TimerIdOffsets.Button + 60 + TimerIdOffsets.Press,</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">        Play_8P_Late = TimerIdOffsets.PlayerJudge + 80 + TimerIdOffsets.Late,</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button6_Release = TimerIdOffsets.Button + 60 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button6_Bomb = TimerIdOffsets.Button + 60 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button6_LongBomb = TimerIdOffsets.Button + 60 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button6_Mine = TimerIdOffsets.Button + 60 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <f t="shared" ref="A38" si="7">A32+1</f>
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button7_Press = TimerIdOffsets.Button + 70 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button7_Release = TimerIdOffsets.Button + 70 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button7_Bomb = TimerIdOffsets.Button + 70 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button7_LongBomb = TimerIdOffsets.Button + 70 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button7_Mine = TimerIdOffsets.Button + 70 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <f t="shared" ref="A44" si="8">A38+1</f>
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button8_Press = TimerIdOffsets.Button + 80 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button8_Release = TimerIdOffsets.Button + 80 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button8_Bomb = TimerIdOffsets.Button + 80 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button8_LongBomb = TimerIdOffsets.Button + 80 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button8_Mine = TimerIdOffsets.Button + 80 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <f t="shared" ref="A50" si="9">A44+1</f>
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button9_Press = TimerIdOffsets.Button + 90 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button9_Release = TimerIdOffsets.Button + 90 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button9_Bomb = TimerIdOffsets.Button + 90 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button9_LongBomb = TimerIdOffsets.Button + 90 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B54" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button9_Mine = TimerIdOffsets.Button + 90 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <f t="shared" ref="A56" si="10">A50+1</f>
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button10_Press = TimerIdOffsets.Button + 100 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button10_Release = TimerIdOffsets.Button + 100 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A58">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button10_Bomb = TimerIdOffsets.Button + 100 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button10_LongBomb = TimerIdOffsets.Button + 100 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button10_Mine = TimerIdOffsets.Button + 100 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C61" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A62">
+        <f t="shared" ref="A62" si="11">A56+1</f>
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button11_Press = TimerIdOffsets.Button + 110 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button11_Release = TimerIdOffsets.Button + 110 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B64" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button11_Bomb = TimerIdOffsets.Button + 110 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B65" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button11_LongBomb = TimerIdOffsets.Button + 110 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">        Play_Button11_Mine = TimerIdOffsets.Button + 110 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C67" t="str">
+        <f t="shared" ref="C67:C130" si="12">IF(A67="","","        Play_Button"&amp;A67&amp;"_"&amp;B67&amp;" = TimerIdOffsets.Button + "&amp;A67&amp;"0 + TimerIdOffsets."&amp;B67&amp;",")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <f t="shared" ref="A68" si="13">A62+1</f>
+        <v>12</v>
+      </c>
+      <c r="B68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button12_Press = TimerIdOffsets.Button + 120 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button12_Release = TimerIdOffsets.Button + 120 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button12_Bomb = TimerIdOffsets.Button + 120 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button12_LongBomb = TimerIdOffsets.Button + 120 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button12_Mine = TimerIdOffsets.Button + 120 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C73" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <f t="shared" ref="A74" si="14">A68+1</f>
+        <v>13</v>
+      </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button13_Press = TimerIdOffsets.Button + 130 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button13_Release = TimerIdOffsets.Button + 130 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button13_Bomb = TimerIdOffsets.Button + 130 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button13_LongBomb = TimerIdOffsets.Button + 130 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <f t="shared" ref="A78:A141" si="15">A72+1</f>
+        <v>13</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button13_Mine = TimerIdOffsets.Button + 130 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C79" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A80">
+        <f t="shared" ref="A80" si="16">A74+1</f>
+        <v>14</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button14_Press = TimerIdOffsets.Button + 140 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A81">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="B81" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button14_Release = TimerIdOffsets.Button + 140 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A82">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="B82" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button14_Bomb = TimerIdOffsets.Button + 140 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="B83" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button14_LongBomb = TimerIdOffsets.Button + 140 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A84">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="B84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button14_Mine = TimerIdOffsets.Button + 140 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C85" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A86">
+        <f t="shared" ref="A86" si="17">A80+1</f>
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button15_Press = TimerIdOffsets.Button + 150 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button15_Release = TimerIdOffsets.Button + 150 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A88">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button15_Bomb = TimerIdOffsets.Button + 150 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button15_LongBomb = TimerIdOffsets.Button + 150 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A90">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button15_Mine = TimerIdOffsets.Button + 150 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C91" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A92">
+        <f t="shared" ref="A92" si="18">A86+1</f>
+        <v>16</v>
+      </c>
+      <c r="B92" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button16_Press = TimerIdOffsets.Button + 160 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="B93" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button16_Release = TimerIdOffsets.Button + 160 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="B94" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button16_Bomb = TimerIdOffsets.Button + 160 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="B95" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button16_LongBomb = TimerIdOffsets.Button + 160 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button16_Mine = TimerIdOffsets.Button + 160 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C97" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <f t="shared" ref="A98" si="19">A92+1</f>
+        <v>17</v>
+      </c>
+      <c r="B98" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button17_Press = TimerIdOffsets.Button + 170 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button17_Release = TimerIdOffsets.Button + 170 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="B100" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button17_Bomb = TimerIdOffsets.Button + 170 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="B101" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button17_LongBomb = TimerIdOffsets.Button + 170 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button17_Mine = TimerIdOffsets.Button + 170 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C103" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <f t="shared" ref="A104" si="20">A98+1</f>
+        <v>18</v>
+      </c>
+      <c r="B104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button18_Press = TimerIdOffsets.Button + 180 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <f t="shared" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button18_Release = TimerIdOffsets.Button + 180 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A106">
+        <f t="shared" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="B106" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button18_Bomb = TimerIdOffsets.Button + 180 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <f t="shared" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="B107" t="s">
+        <v>22</v>
+      </c>
+      <c r="C107" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button18_LongBomb = TimerIdOffsets.Button + 180 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <f t="shared" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="B108" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button18_Mine = TimerIdOffsets.Button + 180 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C109" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <f t="shared" ref="A110" si="21">A104+1</f>
+        <v>19</v>
+      </c>
+      <c r="B110" t="s">
+        <v>19</v>
+      </c>
+      <c r="C110" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button19_Press = TimerIdOffsets.Button + 190 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <f t="shared" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="B111" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button19_Release = TimerIdOffsets.Button + 190 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A112">
+        <f t="shared" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="B112" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button19_Bomb = TimerIdOffsets.Button + 190 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <f t="shared" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="B113" t="s">
+        <v>22</v>
+      </c>
+      <c r="C113" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button19_LongBomb = TimerIdOffsets.Button + 190 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <f t="shared" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>23</v>
+      </c>
+      <c r="C114" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button19_Mine = TimerIdOffsets.Button + 190 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C115" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A116">
+        <f t="shared" ref="A116" si="22">A110+1</f>
+        <v>20</v>
+      </c>
+      <c r="B116" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button20_Press = TimerIdOffsets.Button + 200 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A117">
+        <f t="shared" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="B117" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button20_Release = TimerIdOffsets.Button + 200 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A118">
+        <f t="shared" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="B118" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button20_Bomb = TimerIdOffsets.Button + 200 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A119">
+        <f t="shared" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="B119" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button20_LongBomb = TimerIdOffsets.Button + 200 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <f t="shared" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="B120" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button20_Mine = TimerIdOffsets.Button + 200 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C121" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A122">
+        <f t="shared" ref="A122" si="23">A116+1</f>
+        <v>21</v>
+      </c>
+      <c r="B122" t="s">
+        <v>19</v>
+      </c>
+      <c r="C122" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button21_Press = TimerIdOffsets.Button + 210 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A123">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="B123" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button21_Release = TimerIdOffsets.Button + 210 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A124">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="B124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C124" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button21_Bomb = TimerIdOffsets.Button + 210 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A125">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="B125" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button21_LongBomb = TimerIdOffsets.Button + 210 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A126">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="B126" t="s">
+        <v>23</v>
+      </c>
+      <c r="C126" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button21_Mine = TimerIdOffsets.Button + 210 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C127" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A128">
+        <f t="shared" ref="A128" si="24">A122+1</f>
+        <v>22</v>
+      </c>
+      <c r="B128" t="s">
+        <v>19</v>
+      </c>
+      <c r="C128" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button22_Press = TimerIdOffsets.Button + 220 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A129">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="B129" t="s">
+        <v>20</v>
+      </c>
+      <c r="C129" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button22_Release = TimerIdOffsets.Button + 220 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A130">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="B130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">        Play_Button22_Bomb = TimerIdOffsets.Button + 220 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A131">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="B131" t="s">
+        <v>22</v>
+      </c>
+      <c r="C131" t="str">
+        <f t="shared" ref="C131:C194" si="25">IF(A131="","","        Play_Button"&amp;A131&amp;"_"&amp;B131&amp;" = TimerIdOffsets.Button + "&amp;A131&amp;"0 + TimerIdOffsets."&amp;B131&amp;",")</f>
+        <v xml:space="preserve">        Play_Button22_LongBomb = TimerIdOffsets.Button + 220 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A132">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="B132" t="s">
+        <v>23</v>
+      </c>
+      <c r="C132" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button22_Mine = TimerIdOffsets.Button + 220 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C133" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A134">
+        <f t="shared" ref="A134" si="26">A128+1</f>
+        <v>23</v>
+      </c>
+      <c r="B134" t="s">
+        <v>19</v>
+      </c>
+      <c r="C134" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button23_Press = TimerIdOffsets.Button + 230 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A135">
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+      <c r="B135" t="s">
+        <v>20</v>
+      </c>
+      <c r="C135" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button23_Release = TimerIdOffsets.Button + 230 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A136">
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+      <c r="B136" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button23_Bomb = TimerIdOffsets.Button + 230 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A137">
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+      <c r="B137" t="s">
+        <v>22</v>
+      </c>
+      <c r="C137" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button23_LongBomb = TimerIdOffsets.Button + 230 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A138">
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+      <c r="B138" t="s">
+        <v>23</v>
+      </c>
+      <c r="C138" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button23_Mine = TimerIdOffsets.Button + 230 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C139" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A140">
+        <f t="shared" ref="A140" si="27">A134+1</f>
+        <v>24</v>
+      </c>
+      <c r="B140" t="s">
+        <v>19</v>
+      </c>
+      <c r="C140" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button24_Press = TimerIdOffsets.Button + 240 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A141">
+        <f t="shared" si="15"/>
+        <v>24</v>
+      </c>
+      <c r="B141" t="s">
+        <v>20</v>
+      </c>
+      <c r="C141" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button24_Release = TimerIdOffsets.Button + 240 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A142">
+        <f t="shared" ref="A142:A204" si="28">A136+1</f>
+        <v>24</v>
+      </c>
+      <c r="B142" t="s">
+        <v>21</v>
+      </c>
+      <c r="C142" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button24_Bomb = TimerIdOffsets.Button + 240 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A143">
+        <f t="shared" si="28"/>
+        <v>24</v>
+      </c>
+      <c r="B143" t="s">
+        <v>22</v>
+      </c>
+      <c r="C143" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button24_LongBomb = TimerIdOffsets.Button + 240 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A144">
+        <f t="shared" si="28"/>
+        <v>24</v>
+      </c>
+      <c r="B144" t="s">
+        <v>23</v>
+      </c>
+      <c r="C144" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button24_Mine = TimerIdOffsets.Button + 240 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C145" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A146">
+        <f t="shared" ref="A146" si="29">A140+1</f>
+        <v>25</v>
+      </c>
+      <c r="B146" t="s">
+        <v>19</v>
+      </c>
+      <c r="C146" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button25_Press = TimerIdOffsets.Button + 250 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A147">
+        <f t="shared" si="28"/>
+        <v>25</v>
+      </c>
+      <c r="B147" t="s">
+        <v>20</v>
+      </c>
+      <c r="C147" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button25_Release = TimerIdOffsets.Button + 250 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A148">
+        <f t="shared" si="28"/>
+        <v>25</v>
+      </c>
+      <c r="B148" t="s">
+        <v>21</v>
+      </c>
+      <c r="C148" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button25_Bomb = TimerIdOffsets.Button + 250 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A149">
+        <f t="shared" si="28"/>
+        <v>25</v>
+      </c>
+      <c r="B149" t="s">
+        <v>22</v>
+      </c>
+      <c r="C149" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button25_LongBomb = TimerIdOffsets.Button + 250 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A150">
+        <f t="shared" si="28"/>
+        <v>25</v>
+      </c>
+      <c r="B150" t="s">
+        <v>23</v>
+      </c>
+      <c r="C150" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button25_Mine = TimerIdOffsets.Button + 250 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C151" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A152">
+        <f t="shared" ref="A152" si="30">A146+1</f>
+        <v>26</v>
+      </c>
+      <c r="B152" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button26_Press = TimerIdOffsets.Button + 260 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A153">
+        <f t="shared" si="28"/>
+        <v>26</v>
+      </c>
+      <c r="B153" t="s">
+        <v>20</v>
+      </c>
+      <c r="C153" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button26_Release = TimerIdOffsets.Button + 260 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A154">
+        <f t="shared" si="28"/>
+        <v>26</v>
+      </c>
+      <c r="B154" t="s">
+        <v>21</v>
+      </c>
+      <c r="C154" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button26_Bomb = TimerIdOffsets.Button + 260 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A155">
+        <f t="shared" si="28"/>
+        <v>26</v>
+      </c>
+      <c r="B155" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button26_LongBomb = TimerIdOffsets.Button + 260 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A156">
+        <f t="shared" si="28"/>
+        <v>26</v>
+      </c>
+      <c r="B156" t="s">
+        <v>23</v>
+      </c>
+      <c r="C156" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button26_Mine = TimerIdOffsets.Button + 260 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C157" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A158">
+        <f t="shared" ref="A158" si="31">A152+1</f>
+        <v>27</v>
+      </c>
+      <c r="B158" t="s">
+        <v>19</v>
+      </c>
+      <c r="C158" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button27_Press = TimerIdOffsets.Button + 270 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A159">
+        <f t="shared" si="28"/>
+        <v>27</v>
+      </c>
+      <c r="B159" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button27_Release = TimerIdOffsets.Button + 270 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A160">
+        <f t="shared" si="28"/>
+        <v>27</v>
+      </c>
+      <c r="B160" t="s">
+        <v>21</v>
+      </c>
+      <c r="C160" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button27_Bomb = TimerIdOffsets.Button + 270 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A161">
+        <f t="shared" si="28"/>
+        <v>27</v>
+      </c>
+      <c r="B161" t="s">
+        <v>22</v>
+      </c>
+      <c r="C161" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button27_LongBomb = TimerIdOffsets.Button + 270 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A162">
+        <f t="shared" si="28"/>
+        <v>27</v>
+      </c>
+      <c r="B162" t="s">
+        <v>23</v>
+      </c>
+      <c r="C162" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button27_Mine = TimerIdOffsets.Button + 270 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C163" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A164">
+        <f t="shared" ref="A164" si="32">A158+1</f>
+        <v>28</v>
+      </c>
+      <c r="B164" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button28_Press = TimerIdOffsets.Button + 280 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A165">
+        <f t="shared" si="28"/>
+        <v>28</v>
+      </c>
+      <c r="B165" t="s">
+        <v>20</v>
+      </c>
+      <c r="C165" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button28_Release = TimerIdOffsets.Button + 280 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A166">
+        <f t="shared" si="28"/>
+        <v>28</v>
+      </c>
+      <c r="B166" t="s">
+        <v>21</v>
+      </c>
+      <c r="C166" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button28_Bomb = TimerIdOffsets.Button + 280 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A167">
+        <f t="shared" si="28"/>
+        <v>28</v>
+      </c>
+      <c r="B167" t="s">
+        <v>22</v>
+      </c>
+      <c r="C167" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button28_LongBomb = TimerIdOffsets.Button + 280 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A168">
+        <f t="shared" si="28"/>
+        <v>28</v>
+      </c>
+      <c r="B168" t="s">
+        <v>23</v>
+      </c>
+      <c r="C168" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button28_Mine = TimerIdOffsets.Button + 280 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C169" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A170">
+        <f t="shared" ref="A170" si="33">A164+1</f>
+        <v>29</v>
+      </c>
+      <c r="B170" t="s">
+        <v>19</v>
+      </c>
+      <c r="C170" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button29_Press = TimerIdOffsets.Button + 290 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A171">
+        <f t="shared" si="28"/>
+        <v>29</v>
+      </c>
+      <c r="B171" t="s">
+        <v>20</v>
+      </c>
+      <c r="C171" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button29_Release = TimerIdOffsets.Button + 290 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A172">
+        <f t="shared" si="28"/>
+        <v>29</v>
+      </c>
+      <c r="B172" t="s">
+        <v>21</v>
+      </c>
+      <c r="C172" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button29_Bomb = TimerIdOffsets.Button + 290 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A173">
+        <f t="shared" si="28"/>
+        <v>29</v>
+      </c>
+      <c r="B173" t="s">
+        <v>22</v>
+      </c>
+      <c r="C173" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button29_LongBomb = TimerIdOffsets.Button + 290 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A174">
+        <f t="shared" si="28"/>
+        <v>29</v>
+      </c>
+      <c r="B174" t="s">
+        <v>23</v>
+      </c>
+      <c r="C174" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button29_Mine = TimerIdOffsets.Button + 290 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C175" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A176">
+        <f t="shared" ref="A176" si="34">A170+1</f>
+        <v>30</v>
+      </c>
+      <c r="B176" t="s">
+        <v>19</v>
+      </c>
+      <c r="C176" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button30_Press = TimerIdOffsets.Button + 300 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A177">
+        <f t="shared" si="28"/>
+        <v>30</v>
+      </c>
+      <c r="B177" t="s">
+        <v>20</v>
+      </c>
+      <c r="C177" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button30_Release = TimerIdOffsets.Button + 300 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A178">
+        <f t="shared" si="28"/>
+        <v>30</v>
+      </c>
+      <c r="B178" t="s">
+        <v>21</v>
+      </c>
+      <c r="C178" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button30_Bomb = TimerIdOffsets.Button + 300 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A179">
+        <f t="shared" si="28"/>
+        <v>30</v>
+      </c>
+      <c r="B179" t="s">
+        <v>22</v>
+      </c>
+      <c r="C179" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button30_LongBomb = TimerIdOffsets.Button + 300 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A180">
+        <f t="shared" si="28"/>
+        <v>30</v>
+      </c>
+      <c r="B180" t="s">
+        <v>23</v>
+      </c>
+      <c r="C180" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button30_Mine = TimerIdOffsets.Button + 300 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C181" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A182">
+        <f t="shared" ref="A182" si="35">A176+1</f>
+        <v>31</v>
+      </c>
+      <c r="B182" t="s">
+        <v>19</v>
+      </c>
+      <c r="C182" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button31_Press = TimerIdOffsets.Button + 310 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A183">
+        <f t="shared" si="28"/>
+        <v>31</v>
+      </c>
+      <c r="B183" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button31_Release = TimerIdOffsets.Button + 310 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A184">
+        <f t="shared" si="28"/>
+        <v>31</v>
+      </c>
+      <c r="B184" t="s">
+        <v>21</v>
+      </c>
+      <c r="C184" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button31_Bomb = TimerIdOffsets.Button + 310 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A185">
+        <f t="shared" si="28"/>
+        <v>31</v>
+      </c>
+      <c r="B185" t="s">
+        <v>22</v>
+      </c>
+      <c r="C185" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button31_LongBomb = TimerIdOffsets.Button + 310 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A186">
+        <f t="shared" si="28"/>
+        <v>31</v>
+      </c>
+      <c r="B186" t="s">
+        <v>23</v>
+      </c>
+      <c r="C186" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button31_Mine = TimerIdOffsets.Button + 310 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C187" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A188">
+        <f t="shared" ref="A188" si="36">A182+1</f>
+        <v>32</v>
+      </c>
+      <c r="B188" t="s">
+        <v>19</v>
+      </c>
+      <c r="C188" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button32_Press = TimerIdOffsets.Button + 320 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A189">
+        <f t="shared" si="28"/>
+        <v>32</v>
+      </c>
+      <c r="B189" t="s">
+        <v>20</v>
+      </c>
+      <c r="C189" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button32_Release = TimerIdOffsets.Button + 320 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A190">
+        <f t="shared" si="28"/>
+        <v>32</v>
+      </c>
+      <c r="B190" t="s">
+        <v>21</v>
+      </c>
+      <c r="C190" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button32_Bomb = TimerIdOffsets.Button + 320 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A191">
+        <f t="shared" si="28"/>
+        <v>32</v>
+      </c>
+      <c r="B191" t="s">
+        <v>22</v>
+      </c>
+      <c r="C191" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button32_LongBomb = TimerIdOffsets.Button + 320 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A192">
+        <f t="shared" si="28"/>
+        <v>32</v>
+      </c>
+      <c r="B192" t="s">
+        <v>23</v>
+      </c>
+      <c r="C192" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button32_Mine = TimerIdOffsets.Button + 320 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C193" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A194">
+        <f t="shared" ref="A194" si="37">A188+1</f>
+        <v>33</v>
+      </c>
+      <c r="B194" t="s">
+        <v>19</v>
+      </c>
+      <c r="C194" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">        Play_Button33_Press = TimerIdOffsets.Button + 330 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A195">
+        <f t="shared" si="28"/>
+        <v>33</v>
+      </c>
+      <c r="B195" t="s">
+        <v>20</v>
+      </c>
+      <c r="C195" t="str">
+        <f t="shared" ref="C195:C258" si="38">IF(A195="","","        Play_Button"&amp;A195&amp;"_"&amp;B195&amp;" = TimerIdOffsets.Button + "&amp;A195&amp;"0 + TimerIdOffsets."&amp;B195&amp;",")</f>
+        <v xml:space="preserve">        Play_Button33_Release = TimerIdOffsets.Button + 330 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A196">
+        <f t="shared" si="28"/>
+        <v>33</v>
+      </c>
+      <c r="B196" t="s">
+        <v>21</v>
+      </c>
+      <c r="C196" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button33_Bomb = TimerIdOffsets.Button + 330 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A197">
+        <f t="shared" si="28"/>
+        <v>33</v>
+      </c>
+      <c r="B197" t="s">
+        <v>22</v>
+      </c>
+      <c r="C197" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button33_LongBomb = TimerIdOffsets.Button + 330 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A198">
+        <f t="shared" si="28"/>
+        <v>33</v>
+      </c>
+      <c r="B198" t="s">
+        <v>23</v>
+      </c>
+      <c r="C198" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button33_Mine = TimerIdOffsets.Button + 330 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C199" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A200">
+        <f t="shared" ref="A200" si="39">A194+1</f>
+        <v>34</v>
+      </c>
+      <c r="B200" t="s">
+        <v>19</v>
+      </c>
+      <c r="C200" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button34_Press = TimerIdOffsets.Button + 340 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A201">
+        <f t="shared" si="28"/>
+        <v>34</v>
+      </c>
+      <c r="B201" t="s">
+        <v>20</v>
+      </c>
+      <c r="C201" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button34_Release = TimerIdOffsets.Button + 340 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A202">
+        <f t="shared" si="28"/>
+        <v>34</v>
+      </c>
+      <c r="B202" t="s">
+        <v>21</v>
+      </c>
+      <c r="C202" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button34_Bomb = TimerIdOffsets.Button + 340 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A203">
+        <f t="shared" si="28"/>
+        <v>34</v>
+      </c>
+      <c r="B203" t="s">
+        <v>22</v>
+      </c>
+      <c r="C203" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button34_LongBomb = TimerIdOffsets.Button + 340 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A204">
+        <f t="shared" si="28"/>
+        <v>34</v>
+      </c>
+      <c r="B204" t="s">
+        <v>23</v>
+      </c>
+      <c r="C204" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button34_Mine = TimerIdOffsets.Button + 340 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C205" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A206">
+        <f t="shared" ref="A206:A269" si="40">A200+1</f>
+        <v>35</v>
+      </c>
+      <c r="B206" t="s">
+        <v>19</v>
+      </c>
+      <c r="C206" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button35_Press = TimerIdOffsets.Button + 350 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A207">
+        <f t="shared" si="40"/>
+        <v>35</v>
+      </c>
+      <c r="B207" t="s">
+        <v>20</v>
+      </c>
+      <c r="C207" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button35_Release = TimerIdOffsets.Button + 350 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A208">
+        <f t="shared" si="40"/>
+        <v>35</v>
+      </c>
+      <c r="B208" t="s">
+        <v>21</v>
+      </c>
+      <c r="C208" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button35_Bomb = TimerIdOffsets.Button + 350 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A209">
+        <f t="shared" si="40"/>
+        <v>35</v>
+      </c>
+      <c r="B209" t="s">
+        <v>22</v>
+      </c>
+      <c r="C209" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button35_LongBomb = TimerIdOffsets.Button + 350 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A210">
+        <f t="shared" si="40"/>
+        <v>35</v>
+      </c>
+      <c r="B210" t="s">
+        <v>23</v>
+      </c>
+      <c r="C210" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button35_Mine = TimerIdOffsets.Button + 350 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C211" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A212">
+        <f t="shared" ref="A212" si="41">A206+1</f>
+        <v>36</v>
+      </c>
+      <c r="B212" t="s">
+        <v>19</v>
+      </c>
+      <c r="C212" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button36_Press = TimerIdOffsets.Button + 360 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A213">
+        <f t="shared" si="40"/>
+        <v>36</v>
+      </c>
+      <c r="B213" t="s">
+        <v>20</v>
+      </c>
+      <c r="C213" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button36_Release = TimerIdOffsets.Button + 360 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A214">
+        <f t="shared" si="40"/>
+        <v>36</v>
+      </c>
+      <c r="B214" t="s">
+        <v>21</v>
+      </c>
+      <c r="C214" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button36_Bomb = TimerIdOffsets.Button + 360 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A215">
+        <f t="shared" si="40"/>
+        <v>36</v>
+      </c>
+      <c r="B215" t="s">
+        <v>22</v>
+      </c>
+      <c r="C215" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button36_LongBomb = TimerIdOffsets.Button + 360 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A216">
+        <f t="shared" si="40"/>
+        <v>36</v>
+      </c>
+      <c r="B216" t="s">
+        <v>23</v>
+      </c>
+      <c r="C216" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button36_Mine = TimerIdOffsets.Button + 360 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C217" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A218">
+        <f t="shared" ref="A218" si="42">A212+1</f>
+        <v>37</v>
+      </c>
+      <c r="B218" t="s">
+        <v>19</v>
+      </c>
+      <c r="C218" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button37_Press = TimerIdOffsets.Button + 370 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A219">
+        <f t="shared" si="40"/>
+        <v>37</v>
+      </c>
+      <c r="B219" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button37_Release = TimerIdOffsets.Button + 370 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A220">
+        <f t="shared" si="40"/>
+        <v>37</v>
+      </c>
+      <c r="B220" t="s">
+        <v>21</v>
+      </c>
+      <c r="C220" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button37_Bomb = TimerIdOffsets.Button + 370 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A221">
+        <f t="shared" si="40"/>
+        <v>37</v>
+      </c>
+      <c r="B221" t="s">
+        <v>22</v>
+      </c>
+      <c r="C221" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button37_LongBomb = TimerIdOffsets.Button + 370 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A222">
+        <f t="shared" si="40"/>
+        <v>37</v>
+      </c>
+      <c r="B222" t="s">
+        <v>23</v>
+      </c>
+      <c r="C222" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button37_Mine = TimerIdOffsets.Button + 370 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C223" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A224">
+        <f t="shared" ref="A224" si="43">A218+1</f>
+        <v>38</v>
+      </c>
+      <c r="B224" t="s">
+        <v>19</v>
+      </c>
+      <c r="C224" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button38_Press = TimerIdOffsets.Button + 380 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A225">
+        <f t="shared" si="40"/>
+        <v>38</v>
+      </c>
+      <c r="B225" t="s">
+        <v>20</v>
+      </c>
+      <c r="C225" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button38_Release = TimerIdOffsets.Button + 380 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A226">
+        <f t="shared" si="40"/>
+        <v>38</v>
+      </c>
+      <c r="B226" t="s">
+        <v>21</v>
+      </c>
+      <c r="C226" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button38_Bomb = TimerIdOffsets.Button + 380 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A227">
+        <f t="shared" si="40"/>
+        <v>38</v>
+      </c>
+      <c r="B227" t="s">
+        <v>22</v>
+      </c>
+      <c r="C227" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button38_LongBomb = TimerIdOffsets.Button + 380 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A228">
+        <f t="shared" si="40"/>
+        <v>38</v>
+      </c>
+      <c r="B228" t="s">
+        <v>23</v>
+      </c>
+      <c r="C228" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button38_Mine = TimerIdOffsets.Button + 380 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C229" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A230">
+        <f t="shared" ref="A230" si="44">A224+1</f>
+        <v>39</v>
+      </c>
+      <c r="B230" t="s">
+        <v>19</v>
+      </c>
+      <c r="C230" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button39_Press = TimerIdOffsets.Button + 390 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A231">
+        <f t="shared" si="40"/>
+        <v>39</v>
+      </c>
+      <c r="B231" t="s">
+        <v>20</v>
+      </c>
+      <c r="C231" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button39_Release = TimerIdOffsets.Button + 390 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A232">
+        <f t="shared" si="40"/>
+        <v>39</v>
+      </c>
+      <c r="B232" t="s">
+        <v>21</v>
+      </c>
+      <c r="C232" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button39_Bomb = TimerIdOffsets.Button + 390 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A233">
+        <f t="shared" si="40"/>
+        <v>39</v>
+      </c>
+      <c r="B233" t="s">
+        <v>22</v>
+      </c>
+      <c r="C233" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button39_LongBomb = TimerIdOffsets.Button + 390 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A234">
+        <f t="shared" si="40"/>
+        <v>39</v>
+      </c>
+      <c r="B234" t="s">
+        <v>23</v>
+      </c>
+      <c r="C234" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button39_Mine = TimerIdOffsets.Button + 390 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C235" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A236">
+        <f t="shared" ref="A236" si="45">A230+1</f>
+        <v>40</v>
+      </c>
+      <c r="B236" t="s">
+        <v>19</v>
+      </c>
+      <c r="C236" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button40_Press = TimerIdOffsets.Button + 400 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A237">
+        <f t="shared" si="40"/>
+        <v>40</v>
+      </c>
+      <c r="B237" t="s">
+        <v>20</v>
+      </c>
+      <c r="C237" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button40_Release = TimerIdOffsets.Button + 400 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A238">
+        <f t="shared" si="40"/>
+        <v>40</v>
+      </c>
+      <c r="B238" t="s">
+        <v>21</v>
+      </c>
+      <c r="C238" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button40_Bomb = TimerIdOffsets.Button + 400 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A239">
+        <f t="shared" si="40"/>
+        <v>40</v>
+      </c>
+      <c r="B239" t="s">
+        <v>22</v>
+      </c>
+      <c r="C239" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button40_LongBomb = TimerIdOffsets.Button + 400 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A240">
+        <f t="shared" si="40"/>
+        <v>40</v>
+      </c>
+      <c r="B240" t="s">
+        <v>23</v>
+      </c>
+      <c r="C240" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button40_Mine = TimerIdOffsets.Button + 400 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C241" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A242">
+        <f t="shared" ref="A242" si="46">A236+1</f>
+        <v>41</v>
+      </c>
+      <c r="B242" t="s">
+        <v>19</v>
+      </c>
+      <c r="C242" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button41_Press = TimerIdOffsets.Button + 410 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A243">
+        <f t="shared" si="40"/>
+        <v>41</v>
+      </c>
+      <c r="B243" t="s">
+        <v>20</v>
+      </c>
+      <c r="C243" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button41_Release = TimerIdOffsets.Button + 410 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A244">
+        <f t="shared" si="40"/>
+        <v>41</v>
+      </c>
+      <c r="B244" t="s">
+        <v>21</v>
+      </c>
+      <c r="C244" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button41_Bomb = TimerIdOffsets.Button + 410 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A245">
+        <f t="shared" si="40"/>
+        <v>41</v>
+      </c>
+      <c r="B245" t="s">
+        <v>22</v>
+      </c>
+      <c r="C245" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button41_LongBomb = TimerIdOffsets.Button + 410 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A246">
+        <f t="shared" si="40"/>
+        <v>41</v>
+      </c>
+      <c r="B246" t="s">
+        <v>23</v>
+      </c>
+      <c r="C246" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button41_Mine = TimerIdOffsets.Button + 410 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C247" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A248">
+        <f t="shared" ref="A248" si="47">A242+1</f>
+        <v>42</v>
+      </c>
+      <c r="B248" t="s">
+        <v>19</v>
+      </c>
+      <c r="C248" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button42_Press = TimerIdOffsets.Button + 420 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A249">
+        <f t="shared" si="40"/>
+        <v>42</v>
+      </c>
+      <c r="B249" t="s">
+        <v>20</v>
+      </c>
+      <c r="C249" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button42_Release = TimerIdOffsets.Button + 420 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A250">
+        <f t="shared" si="40"/>
+        <v>42</v>
+      </c>
+      <c r="B250" t="s">
+        <v>21</v>
+      </c>
+      <c r="C250" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button42_Bomb = TimerIdOffsets.Button + 420 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A251">
+        <f t="shared" si="40"/>
+        <v>42</v>
+      </c>
+      <c r="B251" t="s">
+        <v>22</v>
+      </c>
+      <c r="C251" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button42_LongBomb = TimerIdOffsets.Button + 420 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A252">
+        <f t="shared" si="40"/>
+        <v>42</v>
+      </c>
+      <c r="B252" t="s">
+        <v>23</v>
+      </c>
+      <c r="C252" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button42_Mine = TimerIdOffsets.Button + 420 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C253" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A254">
+        <f t="shared" ref="A254" si="48">A248+1</f>
+        <v>43</v>
+      </c>
+      <c r="B254" t="s">
+        <v>19</v>
+      </c>
+      <c r="C254" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button43_Press = TimerIdOffsets.Button + 430 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A255">
+        <f t="shared" si="40"/>
+        <v>43</v>
+      </c>
+      <c r="B255" t="s">
+        <v>20</v>
+      </c>
+      <c r="C255" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button43_Release = TimerIdOffsets.Button + 430 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A256">
+        <f t="shared" si="40"/>
+        <v>43</v>
+      </c>
+      <c r="B256" t="s">
+        <v>21</v>
+      </c>
+      <c r="C256" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button43_Bomb = TimerIdOffsets.Button + 430 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A257">
+        <f t="shared" si="40"/>
+        <v>43</v>
+      </c>
+      <c r="B257" t="s">
+        <v>22</v>
+      </c>
+      <c r="C257" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button43_LongBomb = TimerIdOffsets.Button + 430 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A258">
+        <f t="shared" si="40"/>
+        <v>43</v>
+      </c>
+      <c r="B258" t="s">
+        <v>23</v>
+      </c>
+      <c r="C258" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">        Play_Button43_Mine = TimerIdOffsets.Button + 430 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C259" t="str">
+        <f t="shared" ref="C259:C322" si="49">IF(A259="","","        Play_Button"&amp;A259&amp;"_"&amp;B259&amp;" = TimerIdOffsets.Button + "&amp;A259&amp;"0 + TimerIdOffsets."&amp;B259&amp;",")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A260">
+        <f t="shared" ref="A260" si="50">A254+1</f>
+        <v>44</v>
+      </c>
+      <c r="B260" t="s">
+        <v>19</v>
+      </c>
+      <c r="C260" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button44_Press = TimerIdOffsets.Button + 440 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A261">
+        <f t="shared" si="40"/>
+        <v>44</v>
+      </c>
+      <c r="B261" t="s">
+        <v>20</v>
+      </c>
+      <c r="C261" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button44_Release = TimerIdOffsets.Button + 440 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A262">
+        <f t="shared" si="40"/>
+        <v>44</v>
+      </c>
+      <c r="B262" t="s">
+        <v>21</v>
+      </c>
+      <c r="C262" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button44_Bomb = TimerIdOffsets.Button + 440 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A263">
+        <f t="shared" si="40"/>
+        <v>44</v>
+      </c>
+      <c r="B263" t="s">
+        <v>22</v>
+      </c>
+      <c r="C263" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button44_LongBomb = TimerIdOffsets.Button + 440 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A264">
+        <f t="shared" si="40"/>
+        <v>44</v>
+      </c>
+      <c r="B264" t="s">
+        <v>23</v>
+      </c>
+      <c r="C264" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button44_Mine = TimerIdOffsets.Button + 440 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C265" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A266">
+        <f t="shared" ref="A266" si="51">A260+1</f>
+        <v>45</v>
+      </c>
+      <c r="B266" t="s">
+        <v>19</v>
+      </c>
+      <c r="C266" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button45_Press = TimerIdOffsets.Button + 450 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A267">
+        <f t="shared" si="40"/>
+        <v>45</v>
+      </c>
+      <c r="B267" t="s">
+        <v>20</v>
+      </c>
+      <c r="C267" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button45_Release = TimerIdOffsets.Button + 450 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A268">
+        <f t="shared" si="40"/>
+        <v>45</v>
+      </c>
+      <c r="B268" t="s">
+        <v>21</v>
+      </c>
+      <c r="C268" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button45_Bomb = TimerIdOffsets.Button + 450 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A269">
+        <f t="shared" si="40"/>
+        <v>45</v>
+      </c>
+      <c r="B269" t="s">
+        <v>22</v>
+      </c>
+      <c r="C269" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button45_LongBomb = TimerIdOffsets.Button + 450 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A270">
+        <f t="shared" ref="A270:A333" si="52">A264+1</f>
+        <v>45</v>
+      </c>
+      <c r="B270" t="s">
+        <v>23</v>
+      </c>
+      <c r="C270" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button45_Mine = TimerIdOffsets.Button + 450 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C271" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A272">
+        <f t="shared" ref="A272" si="53">A266+1</f>
+        <v>46</v>
+      </c>
+      <c r="B272" t="s">
+        <v>19</v>
+      </c>
+      <c r="C272" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button46_Press = TimerIdOffsets.Button + 460 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A273">
+        <f t="shared" si="52"/>
+        <v>46</v>
+      </c>
+      <c r="B273" t="s">
+        <v>20</v>
+      </c>
+      <c r="C273" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button46_Release = TimerIdOffsets.Button + 460 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A274">
+        <f t="shared" si="52"/>
+        <v>46</v>
+      </c>
+      <c r="B274" t="s">
+        <v>21</v>
+      </c>
+      <c r="C274" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button46_Bomb = TimerIdOffsets.Button + 460 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A275">
+        <f t="shared" si="52"/>
+        <v>46</v>
+      </c>
+      <c r="B275" t="s">
+        <v>22</v>
+      </c>
+      <c r="C275" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button46_LongBomb = TimerIdOffsets.Button + 460 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A276">
+        <f t="shared" si="52"/>
+        <v>46</v>
+      </c>
+      <c r="B276" t="s">
+        <v>23</v>
+      </c>
+      <c r="C276" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button46_Mine = TimerIdOffsets.Button + 460 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C277" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A278">
+        <f t="shared" ref="A278" si="54">A272+1</f>
+        <v>47</v>
+      </c>
+      <c r="B278" t="s">
+        <v>19</v>
+      </c>
+      <c r="C278" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button47_Press = TimerIdOffsets.Button + 470 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A279">
+        <f t="shared" si="52"/>
+        <v>47</v>
+      </c>
+      <c r="B279" t="s">
+        <v>20</v>
+      </c>
+      <c r="C279" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button47_Release = TimerIdOffsets.Button + 470 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A280">
+        <f t="shared" si="52"/>
+        <v>47</v>
+      </c>
+      <c r="B280" t="s">
+        <v>21</v>
+      </c>
+      <c r="C280" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button47_Bomb = TimerIdOffsets.Button + 470 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A281">
+        <f t="shared" si="52"/>
+        <v>47</v>
+      </c>
+      <c r="B281" t="s">
+        <v>22</v>
+      </c>
+      <c r="C281" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button47_LongBomb = TimerIdOffsets.Button + 470 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A282">
+        <f t="shared" si="52"/>
+        <v>47</v>
+      </c>
+      <c r="B282" t="s">
+        <v>23</v>
+      </c>
+      <c r="C282" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button47_Mine = TimerIdOffsets.Button + 470 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C283" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A284">
+        <f t="shared" ref="A284" si="55">A278+1</f>
+        <v>48</v>
+      </c>
+      <c r="B284" t="s">
+        <v>19</v>
+      </c>
+      <c r="C284" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button48_Press = TimerIdOffsets.Button + 480 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A285">
+        <f t="shared" si="52"/>
+        <v>48</v>
+      </c>
+      <c r="B285" t="s">
+        <v>20</v>
+      </c>
+      <c r="C285" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button48_Release = TimerIdOffsets.Button + 480 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A286">
+        <f t="shared" si="52"/>
+        <v>48</v>
+      </c>
+      <c r="B286" t="s">
+        <v>21</v>
+      </c>
+      <c r="C286" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button48_Bomb = TimerIdOffsets.Button + 480 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A287">
+        <f t="shared" si="52"/>
+        <v>48</v>
+      </c>
+      <c r="B287" t="s">
+        <v>22</v>
+      </c>
+      <c r="C287" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button48_LongBomb = TimerIdOffsets.Button + 480 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A288">
+        <f t="shared" si="52"/>
+        <v>48</v>
+      </c>
+      <c r="B288" t="s">
+        <v>23</v>
+      </c>
+      <c r="C288" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button48_Mine = TimerIdOffsets.Button + 480 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C289" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A290">
+        <f t="shared" ref="A290" si="56">A284+1</f>
+        <v>49</v>
+      </c>
+      <c r="B290" t="s">
+        <v>19</v>
+      </c>
+      <c r="C290" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button49_Press = TimerIdOffsets.Button + 490 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A291">
+        <f t="shared" si="52"/>
+        <v>49</v>
+      </c>
+      <c r="B291" t="s">
+        <v>20</v>
+      </c>
+      <c r="C291" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button49_Release = TimerIdOffsets.Button + 490 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A292">
+        <f t="shared" si="52"/>
+        <v>49</v>
+      </c>
+      <c r="B292" t="s">
+        <v>21</v>
+      </c>
+      <c r="C292" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button49_Bomb = TimerIdOffsets.Button + 490 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A293">
+        <f t="shared" si="52"/>
+        <v>49</v>
+      </c>
+      <c r="B293" t="s">
+        <v>22</v>
+      </c>
+      <c r="C293" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button49_LongBomb = TimerIdOffsets.Button + 490 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A294">
+        <f t="shared" si="52"/>
+        <v>49</v>
+      </c>
+      <c r="B294" t="s">
+        <v>23</v>
+      </c>
+      <c r="C294" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button49_Mine = TimerIdOffsets.Button + 490 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C295" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A296">
+        <f t="shared" ref="A296" si="57">A290+1</f>
+        <v>50</v>
+      </c>
+      <c r="B296" t="s">
+        <v>19</v>
+      </c>
+      <c r="C296" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button50_Press = TimerIdOffsets.Button + 500 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A297">
+        <f t="shared" si="52"/>
+        <v>50</v>
+      </c>
+      <c r="B297" t="s">
+        <v>20</v>
+      </c>
+      <c r="C297" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button50_Release = TimerIdOffsets.Button + 500 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A298">
+        <f t="shared" si="52"/>
+        <v>50</v>
+      </c>
+      <c r="B298" t="s">
+        <v>21</v>
+      </c>
+      <c r="C298" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button50_Bomb = TimerIdOffsets.Button + 500 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A299">
+        <f t="shared" si="52"/>
+        <v>50</v>
+      </c>
+      <c r="B299" t="s">
+        <v>22</v>
+      </c>
+      <c r="C299" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button50_LongBomb = TimerIdOffsets.Button + 500 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A300">
+        <f t="shared" si="52"/>
+        <v>50</v>
+      </c>
+      <c r="B300" t="s">
+        <v>23</v>
+      </c>
+      <c r="C300" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button50_Mine = TimerIdOffsets.Button + 500 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C301" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A302">
+        <f t="shared" ref="A302" si="58">A296+1</f>
+        <v>51</v>
+      </c>
+      <c r="B302" t="s">
+        <v>19</v>
+      </c>
+      <c r="C302" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button51_Press = TimerIdOffsets.Button + 510 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A303">
+        <f t="shared" si="52"/>
+        <v>51</v>
+      </c>
+      <c r="B303" t="s">
+        <v>20</v>
+      </c>
+      <c r="C303" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button51_Release = TimerIdOffsets.Button + 510 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A304">
+        <f t="shared" si="52"/>
+        <v>51</v>
+      </c>
+      <c r="B304" t="s">
+        <v>21</v>
+      </c>
+      <c r="C304" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button51_Bomb = TimerIdOffsets.Button + 510 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A305">
+        <f t="shared" si="52"/>
+        <v>51</v>
+      </c>
+      <c r="B305" t="s">
+        <v>22</v>
+      </c>
+      <c r="C305" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button51_LongBomb = TimerIdOffsets.Button + 510 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A306">
+        <f t="shared" si="52"/>
+        <v>51</v>
+      </c>
+      <c r="B306" t="s">
+        <v>23</v>
+      </c>
+      <c r="C306" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button51_Mine = TimerIdOffsets.Button + 510 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C307" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A308">
+        <f t="shared" ref="A308" si="59">A302+1</f>
+        <v>52</v>
+      </c>
+      <c r="B308" t="s">
+        <v>19</v>
+      </c>
+      <c r="C308" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button52_Press = TimerIdOffsets.Button + 520 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A309">
+        <f t="shared" si="52"/>
+        <v>52</v>
+      </c>
+      <c r="B309" t="s">
+        <v>20</v>
+      </c>
+      <c r="C309" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button52_Release = TimerIdOffsets.Button + 520 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A310">
+        <f t="shared" si="52"/>
+        <v>52</v>
+      </c>
+      <c r="B310" t="s">
+        <v>21</v>
+      </c>
+      <c r="C310" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button52_Bomb = TimerIdOffsets.Button + 520 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A311">
+        <f t="shared" si="52"/>
+        <v>52</v>
+      </c>
+      <c r="B311" t="s">
+        <v>22</v>
+      </c>
+      <c r="C311" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button52_LongBomb = TimerIdOffsets.Button + 520 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A312">
+        <f t="shared" si="52"/>
+        <v>52</v>
+      </c>
+      <c r="B312" t="s">
+        <v>23</v>
+      </c>
+      <c r="C312" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button52_Mine = TimerIdOffsets.Button + 520 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C313" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A314">
+        <f t="shared" ref="A314" si="60">A308+1</f>
+        <v>53</v>
+      </c>
+      <c r="B314" t="s">
+        <v>19</v>
+      </c>
+      <c r="C314" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button53_Press = TimerIdOffsets.Button + 530 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A315">
+        <f t="shared" si="52"/>
+        <v>53</v>
+      </c>
+      <c r="B315" t="s">
+        <v>20</v>
+      </c>
+      <c r="C315" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button53_Release = TimerIdOffsets.Button + 530 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A316">
+        <f t="shared" si="52"/>
+        <v>53</v>
+      </c>
+      <c r="B316" t="s">
+        <v>21</v>
+      </c>
+      <c r="C316" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button53_Bomb = TimerIdOffsets.Button + 530 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A317">
+        <f t="shared" si="52"/>
+        <v>53</v>
+      </c>
+      <c r="B317" t="s">
+        <v>22</v>
+      </c>
+      <c r="C317" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button53_LongBomb = TimerIdOffsets.Button + 530 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A318">
+        <f t="shared" si="52"/>
+        <v>53</v>
+      </c>
+      <c r="B318" t="s">
+        <v>23</v>
+      </c>
+      <c r="C318" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button53_Mine = TimerIdOffsets.Button + 530 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C319" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A320">
+        <f t="shared" ref="A320" si="61">A314+1</f>
+        <v>54</v>
+      </c>
+      <c r="B320" t="s">
+        <v>19</v>
+      </c>
+      <c r="C320" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button54_Press = TimerIdOffsets.Button + 540 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A321">
+        <f t="shared" si="52"/>
+        <v>54</v>
+      </c>
+      <c r="B321" t="s">
+        <v>20</v>
+      </c>
+      <c r="C321" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button54_Release = TimerIdOffsets.Button + 540 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A322">
+        <f t="shared" si="52"/>
+        <v>54</v>
+      </c>
+      <c r="B322" t="s">
+        <v>21</v>
+      </c>
+      <c r="C322" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">        Play_Button54_Bomb = TimerIdOffsets.Button + 540 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A323">
+        <f t="shared" si="52"/>
+        <v>54</v>
+      </c>
+      <c r="B323" t="s">
+        <v>22</v>
+      </c>
+      <c r="C323" t="str">
+        <f t="shared" ref="C323:C386" si="62">IF(A323="","","        Play_Button"&amp;A323&amp;"_"&amp;B323&amp;" = TimerIdOffsets.Button + "&amp;A323&amp;"0 + TimerIdOffsets."&amp;B323&amp;",")</f>
+        <v xml:space="preserve">        Play_Button54_LongBomb = TimerIdOffsets.Button + 540 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A324">
+        <f t="shared" si="52"/>
+        <v>54</v>
+      </c>
+      <c r="B324" t="s">
+        <v>23</v>
+      </c>
+      <c r="C324" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button54_Mine = TimerIdOffsets.Button + 540 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C325" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A326">
+        <f t="shared" ref="A326" si="63">A320+1</f>
+        <v>55</v>
+      </c>
+      <c r="B326" t="s">
+        <v>19</v>
+      </c>
+      <c r="C326" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button55_Press = TimerIdOffsets.Button + 550 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A327">
+        <f t="shared" si="52"/>
+        <v>55</v>
+      </c>
+      <c r="B327" t="s">
+        <v>20</v>
+      </c>
+      <c r="C327" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button55_Release = TimerIdOffsets.Button + 550 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A328">
+        <f t="shared" si="52"/>
+        <v>55</v>
+      </c>
+      <c r="B328" t="s">
+        <v>21</v>
+      </c>
+      <c r="C328" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button55_Bomb = TimerIdOffsets.Button + 550 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A329">
+        <f t="shared" si="52"/>
+        <v>55</v>
+      </c>
+      <c r="B329" t="s">
+        <v>22</v>
+      </c>
+      <c r="C329" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button55_LongBomb = TimerIdOffsets.Button + 550 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A330">
+        <f t="shared" si="52"/>
+        <v>55</v>
+      </c>
+      <c r="B330" t="s">
+        <v>23</v>
+      </c>
+      <c r="C330" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button55_Mine = TimerIdOffsets.Button + 550 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C331" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A332">
+        <f t="shared" ref="A332" si="64">A326+1</f>
+        <v>56</v>
+      </c>
+      <c r="B332" t="s">
+        <v>19</v>
+      </c>
+      <c r="C332" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button56_Press = TimerIdOffsets.Button + 560 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A333">
+        <f t="shared" si="52"/>
+        <v>56</v>
+      </c>
+      <c r="B333" t="s">
+        <v>20</v>
+      </c>
+      <c r="C333" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button56_Release = TimerIdOffsets.Button + 560 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A334">
+        <f t="shared" ref="A334:A396" si="65">A328+1</f>
+        <v>56</v>
+      </c>
+      <c r="B334" t="s">
+        <v>21</v>
+      </c>
+      <c r="C334" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button56_Bomb = TimerIdOffsets.Button + 560 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A335">
+        <f t="shared" si="65"/>
+        <v>56</v>
+      </c>
+      <c r="B335" t="s">
+        <v>22</v>
+      </c>
+      <c r="C335" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button56_LongBomb = TimerIdOffsets.Button + 560 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A336">
+        <f t="shared" si="65"/>
+        <v>56</v>
+      </c>
+      <c r="B336" t="s">
+        <v>23</v>
+      </c>
+      <c r="C336" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button56_Mine = TimerIdOffsets.Button + 560 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C337" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A338">
+        <f t="shared" ref="A338" si="66">A332+1</f>
+        <v>57</v>
+      </c>
+      <c r="B338" t="s">
+        <v>19</v>
+      </c>
+      <c r="C338" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button57_Press = TimerIdOffsets.Button + 570 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A339">
+        <f t="shared" si="65"/>
+        <v>57</v>
+      </c>
+      <c r="B339" t="s">
+        <v>20</v>
+      </c>
+      <c r="C339" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button57_Release = TimerIdOffsets.Button + 570 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A340">
+        <f t="shared" si="65"/>
+        <v>57</v>
+      </c>
+      <c r="B340" t="s">
+        <v>21</v>
+      </c>
+      <c r="C340" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button57_Bomb = TimerIdOffsets.Button + 570 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A341">
+        <f t="shared" si="65"/>
+        <v>57</v>
+      </c>
+      <c r="B341" t="s">
+        <v>22</v>
+      </c>
+      <c r="C341" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button57_LongBomb = TimerIdOffsets.Button + 570 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A342">
+        <f t="shared" si="65"/>
+        <v>57</v>
+      </c>
+      <c r="B342" t="s">
+        <v>23</v>
+      </c>
+      <c r="C342" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button57_Mine = TimerIdOffsets.Button + 570 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C343" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A344">
+        <f t="shared" ref="A344" si="67">A338+1</f>
+        <v>58</v>
+      </c>
+      <c r="B344" t="s">
+        <v>19</v>
+      </c>
+      <c r="C344" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button58_Press = TimerIdOffsets.Button + 580 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A345">
+        <f t="shared" si="65"/>
+        <v>58</v>
+      </c>
+      <c r="B345" t="s">
+        <v>20</v>
+      </c>
+      <c r="C345" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button58_Release = TimerIdOffsets.Button + 580 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A346">
+        <f t="shared" si="65"/>
+        <v>58</v>
+      </c>
+      <c r="B346" t="s">
+        <v>21</v>
+      </c>
+      <c r="C346" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button58_Bomb = TimerIdOffsets.Button + 580 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A347">
+        <f t="shared" si="65"/>
+        <v>58</v>
+      </c>
+      <c r="B347" t="s">
+        <v>22</v>
+      </c>
+      <c r="C347" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button58_LongBomb = TimerIdOffsets.Button + 580 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A348">
+        <f t="shared" si="65"/>
+        <v>58</v>
+      </c>
+      <c r="B348" t="s">
+        <v>23</v>
+      </c>
+      <c r="C348" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button58_Mine = TimerIdOffsets.Button + 580 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C349" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A350">
+        <f t="shared" ref="A350" si="68">A344+1</f>
+        <v>59</v>
+      </c>
+      <c r="B350" t="s">
+        <v>19</v>
+      </c>
+      <c r="C350" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button59_Press = TimerIdOffsets.Button + 590 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A351">
+        <f t="shared" si="65"/>
+        <v>59</v>
+      </c>
+      <c r="B351" t="s">
+        <v>20</v>
+      </c>
+      <c r="C351" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button59_Release = TimerIdOffsets.Button + 590 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A352">
+        <f t="shared" si="65"/>
+        <v>59</v>
+      </c>
+      <c r="B352" t="s">
+        <v>21</v>
+      </c>
+      <c r="C352" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button59_Bomb = TimerIdOffsets.Button + 590 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A353">
+        <f t="shared" si="65"/>
+        <v>59</v>
+      </c>
+      <c r="B353" t="s">
+        <v>22</v>
+      </c>
+      <c r="C353" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button59_LongBomb = TimerIdOffsets.Button + 590 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A354">
+        <f t="shared" si="65"/>
+        <v>59</v>
+      </c>
+      <c r="B354" t="s">
+        <v>23</v>
+      </c>
+      <c r="C354" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button59_Mine = TimerIdOffsets.Button + 590 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C355" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A356">
+        <f t="shared" ref="A356" si="69">A350+1</f>
+        <v>60</v>
+      </c>
+      <c r="B356" t="s">
+        <v>19</v>
+      </c>
+      <c r="C356" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button60_Press = TimerIdOffsets.Button + 600 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A357">
+        <f t="shared" si="65"/>
+        <v>60</v>
+      </c>
+      <c r="B357" t="s">
+        <v>20</v>
+      </c>
+      <c r="C357" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button60_Release = TimerIdOffsets.Button + 600 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A358">
+        <f t="shared" si="65"/>
+        <v>60</v>
+      </c>
+      <c r="B358" t="s">
+        <v>21</v>
+      </c>
+      <c r="C358" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button60_Bomb = TimerIdOffsets.Button + 600 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A359">
+        <f t="shared" si="65"/>
+        <v>60</v>
+      </c>
+      <c r="B359" t="s">
+        <v>22</v>
+      </c>
+      <c r="C359" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button60_LongBomb = TimerIdOffsets.Button + 600 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A360">
+        <f t="shared" si="65"/>
+        <v>60</v>
+      </c>
+      <c r="B360" t="s">
+        <v>23</v>
+      </c>
+      <c r="C360" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button60_Mine = TimerIdOffsets.Button + 600 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C361" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A362">
+        <f t="shared" ref="A362" si="70">A356+1</f>
+        <v>61</v>
+      </c>
+      <c r="B362" t="s">
+        <v>19</v>
+      </c>
+      <c r="C362" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button61_Press = TimerIdOffsets.Button + 610 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A363">
+        <f t="shared" si="65"/>
+        <v>61</v>
+      </c>
+      <c r="B363" t="s">
+        <v>20</v>
+      </c>
+      <c r="C363" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button61_Release = TimerIdOffsets.Button + 610 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A364">
+        <f t="shared" si="65"/>
+        <v>61</v>
+      </c>
+      <c r="B364" t="s">
+        <v>21</v>
+      </c>
+      <c r="C364" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button61_Bomb = TimerIdOffsets.Button + 610 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A365">
+        <f t="shared" si="65"/>
+        <v>61</v>
+      </c>
+      <c r="B365" t="s">
+        <v>22</v>
+      </c>
+      <c r="C365" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button61_LongBomb = TimerIdOffsets.Button + 610 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A366">
+        <f t="shared" si="65"/>
+        <v>61</v>
+      </c>
+      <c r="B366" t="s">
+        <v>23</v>
+      </c>
+      <c r="C366" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button61_Mine = TimerIdOffsets.Button + 610 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C367" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A368">
+        <f t="shared" ref="A368:A426" si="71">A362+1</f>
+        <v>62</v>
+      </c>
+      <c r="B368" t="s">
+        <v>19</v>
+      </c>
+      <c r="C368" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button62_Press = TimerIdOffsets.Button + 620 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A369">
+        <f t="shared" si="65"/>
+        <v>62</v>
+      </c>
+      <c r="B369" t="s">
+        <v>20</v>
+      </c>
+      <c r="C369" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button62_Release = TimerIdOffsets.Button + 620 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A370">
+        <f t="shared" si="65"/>
+        <v>62</v>
+      </c>
+      <c r="B370" t="s">
+        <v>21</v>
+      </c>
+      <c r="C370" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button62_Bomb = TimerIdOffsets.Button + 620 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A371">
+        <f t="shared" si="65"/>
+        <v>62</v>
+      </c>
+      <c r="B371" t="s">
+        <v>22</v>
+      </c>
+      <c r="C371" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button62_LongBomb = TimerIdOffsets.Button + 620 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A372">
+        <f t="shared" si="65"/>
+        <v>62</v>
+      </c>
+      <c r="B372" t="s">
+        <v>23</v>
+      </c>
+      <c r="C372" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button62_Mine = TimerIdOffsets.Button + 620 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C373" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A374">
+        <f t="shared" si="71"/>
+        <v>63</v>
+      </c>
+      <c r="B374" t="s">
+        <v>19</v>
+      </c>
+      <c r="C374" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button63_Press = TimerIdOffsets.Button + 630 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A375">
+        <f t="shared" si="65"/>
+        <v>63</v>
+      </c>
+      <c r="B375" t="s">
+        <v>20</v>
+      </c>
+      <c r="C375" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button63_Release = TimerIdOffsets.Button + 630 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A376">
+        <f t="shared" si="65"/>
+        <v>63</v>
+      </c>
+      <c r="B376" t="s">
+        <v>21</v>
+      </c>
+      <c r="C376" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button63_Bomb = TimerIdOffsets.Button + 630 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A377">
+        <f t="shared" si="65"/>
+        <v>63</v>
+      </c>
+      <c r="B377" t="s">
+        <v>22</v>
+      </c>
+      <c r="C377" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button63_LongBomb = TimerIdOffsets.Button + 630 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A378">
+        <f t="shared" si="65"/>
+        <v>63</v>
+      </c>
+      <c r="B378" t="s">
+        <v>23</v>
+      </c>
+      <c r="C378" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button63_Mine = TimerIdOffsets.Button + 630 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C379" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A380">
+        <f t="shared" si="71"/>
+        <v>64</v>
+      </c>
+      <c r="B380" t="s">
+        <v>19</v>
+      </c>
+      <c r="C380" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button64_Press = TimerIdOffsets.Button + 640 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A381">
+        <f t="shared" si="65"/>
+        <v>64</v>
+      </c>
+      <c r="B381" t="s">
+        <v>20</v>
+      </c>
+      <c r="C381" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button64_Release = TimerIdOffsets.Button + 640 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A382">
+        <f t="shared" si="65"/>
+        <v>64</v>
+      </c>
+      <c r="B382" t="s">
+        <v>21</v>
+      </c>
+      <c r="C382" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button64_Bomb = TimerIdOffsets.Button + 640 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A383">
+        <f t="shared" si="65"/>
+        <v>64</v>
+      </c>
+      <c r="B383" t="s">
+        <v>22</v>
+      </c>
+      <c r="C383" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button64_LongBomb = TimerIdOffsets.Button + 640 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A384">
+        <f t="shared" si="65"/>
+        <v>64</v>
+      </c>
+      <c r="B384" t="s">
+        <v>23</v>
+      </c>
+      <c r="C384" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button64_Mine = TimerIdOffsets.Button + 640 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C385" t="str">
+        <f t="shared" si="62"/>
+        <v/>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A386">
+        <f t="shared" si="71"/>
+        <v>65</v>
+      </c>
+      <c r="B386" t="s">
+        <v>19</v>
+      </c>
+      <c r="C386" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">        Play_Button65_Press = TimerIdOffsets.Button + 650 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A387">
+        <f t="shared" si="65"/>
+        <v>65</v>
+      </c>
+      <c r="B387" t="s">
+        <v>20</v>
+      </c>
+      <c r="C387" t="str">
+        <f t="shared" ref="C387:C426" si="72">IF(A387="","","        Play_Button"&amp;A387&amp;"_"&amp;B387&amp;" = TimerIdOffsets.Button + "&amp;A387&amp;"0 + TimerIdOffsets."&amp;B387&amp;",")</f>
+        <v xml:space="preserve">        Play_Button65_Release = TimerIdOffsets.Button + 650 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A388">
+        <f t="shared" si="65"/>
+        <v>65</v>
+      </c>
+      <c r="B388" t="s">
+        <v>21</v>
+      </c>
+      <c r="C388" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button65_Bomb = TimerIdOffsets.Button + 650 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A389">
+        <f t="shared" si="65"/>
+        <v>65</v>
+      </c>
+      <c r="B389" t="s">
+        <v>22</v>
+      </c>
+      <c r="C389" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button65_LongBomb = TimerIdOffsets.Button + 650 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A390">
+        <f t="shared" si="65"/>
+        <v>65</v>
+      </c>
+      <c r="B390" t="s">
+        <v>23</v>
+      </c>
+      <c r="C390" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button65_Mine = TimerIdOffsets.Button + 650 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C391" t="str">
+        <f t="shared" si="72"/>
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A392">
+        <f t="shared" si="71"/>
+        <v>66</v>
+      </c>
+      <c r="B392" t="s">
+        <v>19</v>
+      </c>
+      <c r="C392" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button66_Press = TimerIdOffsets.Button + 660 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A393">
+        <f t="shared" si="65"/>
+        <v>66</v>
+      </c>
+      <c r="B393" t="s">
+        <v>20</v>
+      </c>
+      <c r="C393" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button66_Release = TimerIdOffsets.Button + 660 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A394">
+        <f t="shared" si="65"/>
+        <v>66</v>
+      </c>
+      <c r="B394" t="s">
+        <v>21</v>
+      </c>
+      <c r="C394" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button66_Bomb = TimerIdOffsets.Button + 660 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A395">
+        <f t="shared" si="65"/>
+        <v>66</v>
+      </c>
+      <c r="B395" t="s">
+        <v>22</v>
+      </c>
+      <c r="C395" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button66_LongBomb = TimerIdOffsets.Button + 660 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A396">
+        <f t="shared" si="65"/>
+        <v>66</v>
+      </c>
+      <c r="B396" t="s">
+        <v>23</v>
+      </c>
+      <c r="C396" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button66_Mine = TimerIdOffsets.Button + 660 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C397" t="str">
+        <f t="shared" si="72"/>
+        <v/>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A398">
+        <f t="shared" si="71"/>
+        <v>67</v>
+      </c>
+      <c r="B398" t="s">
+        <v>19</v>
+      </c>
+      <c r="C398" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button67_Press = TimerIdOffsets.Button + 670 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A399">
+        <f t="shared" si="71"/>
+        <v>67</v>
+      </c>
+      <c r="B399" t="s">
+        <v>20</v>
+      </c>
+      <c r="C399" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button67_Release = TimerIdOffsets.Button + 670 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A400">
+        <f t="shared" si="71"/>
+        <v>67</v>
+      </c>
+      <c r="B400" t="s">
+        <v>21</v>
+      </c>
+      <c r="C400" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button67_Bomb = TimerIdOffsets.Button + 670 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A401">
+        <f t="shared" si="71"/>
+        <v>67</v>
+      </c>
+      <c r="B401" t="s">
+        <v>22</v>
+      </c>
+      <c r="C401" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button67_LongBomb = TimerIdOffsets.Button + 670 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A402">
+        <f t="shared" si="71"/>
+        <v>67</v>
+      </c>
+      <c r="B402" t="s">
+        <v>23</v>
+      </c>
+      <c r="C402" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button67_Mine = TimerIdOffsets.Button + 670 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C403" t="str">
+        <f t="shared" si="72"/>
+        <v/>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A404">
+        <f t="shared" si="71"/>
+        <v>68</v>
+      </c>
+      <c r="B404" t="s">
+        <v>19</v>
+      </c>
+      <c r="C404" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button68_Press = TimerIdOffsets.Button + 680 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A405">
+        <f t="shared" si="71"/>
+        <v>68</v>
+      </c>
+      <c r="B405" t="s">
+        <v>20</v>
+      </c>
+      <c r="C405" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button68_Release = TimerIdOffsets.Button + 680 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A406">
+        <f t="shared" si="71"/>
+        <v>68</v>
+      </c>
+      <c r="B406" t="s">
+        <v>21</v>
+      </c>
+      <c r="C406" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button68_Bomb = TimerIdOffsets.Button + 680 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A407">
+        <f t="shared" si="71"/>
+        <v>68</v>
+      </c>
+      <c r="B407" t="s">
+        <v>22</v>
+      </c>
+      <c r="C407" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button68_LongBomb = TimerIdOffsets.Button + 680 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A408">
+        <f t="shared" si="71"/>
+        <v>68</v>
+      </c>
+      <c r="B408" t="s">
+        <v>23</v>
+      </c>
+      <c r="C408" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button68_Mine = TimerIdOffsets.Button + 680 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C409" t="str">
+        <f t="shared" si="72"/>
+        <v/>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A410">
+        <f t="shared" si="71"/>
+        <v>69</v>
+      </c>
+      <c r="B410" t="s">
+        <v>19</v>
+      </c>
+      <c r="C410" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button69_Press = TimerIdOffsets.Button + 690 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A411">
+        <f t="shared" si="71"/>
+        <v>69</v>
+      </c>
+      <c r="B411" t="s">
+        <v>20</v>
+      </c>
+      <c r="C411" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button69_Release = TimerIdOffsets.Button + 690 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A412">
+        <f t="shared" si="71"/>
+        <v>69</v>
+      </c>
+      <c r="B412" t="s">
+        <v>21</v>
+      </c>
+      <c r="C412" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button69_Bomb = TimerIdOffsets.Button + 690 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A413">
+        <f t="shared" si="71"/>
+        <v>69</v>
+      </c>
+      <c r="B413" t="s">
+        <v>22</v>
+      </c>
+      <c r="C413" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button69_LongBomb = TimerIdOffsets.Button + 690 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A414">
+        <f t="shared" si="71"/>
+        <v>69</v>
+      </c>
+      <c r="B414" t="s">
+        <v>23</v>
+      </c>
+      <c r="C414" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button69_Mine = TimerIdOffsets.Button + 690 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C415" t="str">
+        <f t="shared" si="72"/>
+        <v/>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A416">
+        <f t="shared" si="71"/>
+        <v>70</v>
+      </c>
+      <c r="B416" t="s">
+        <v>19</v>
+      </c>
+      <c r="C416" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button70_Press = TimerIdOffsets.Button + 700 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A417">
+        <f t="shared" si="71"/>
+        <v>70</v>
+      </c>
+      <c r="B417" t="s">
+        <v>20</v>
+      </c>
+      <c r="C417" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button70_Release = TimerIdOffsets.Button + 700 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A418">
+        <f t="shared" si="71"/>
+        <v>70</v>
+      </c>
+      <c r="B418" t="s">
+        <v>21</v>
+      </c>
+      <c r="C418" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button70_Bomb = TimerIdOffsets.Button + 700 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A419">
+        <f t="shared" si="71"/>
+        <v>70</v>
+      </c>
+      <c r="B419" t="s">
+        <v>22</v>
+      </c>
+      <c r="C419" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button70_LongBomb = TimerIdOffsets.Button + 700 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A420">
+        <f t="shared" si="71"/>
+        <v>70</v>
+      </c>
+      <c r="B420" t="s">
+        <v>23</v>
+      </c>
+      <c r="C420" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button70_Mine = TimerIdOffsets.Button + 700 + TimerIdOffsets.Mine,</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C421" t="str">
+        <f t="shared" si="72"/>
+        <v/>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A422">
+        <f t="shared" si="71"/>
+        <v>71</v>
+      </c>
+      <c r="B422" t="s">
+        <v>19</v>
+      </c>
+      <c r="C422" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button71_Press = TimerIdOffsets.Button + 710 + TimerIdOffsets.Press,</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A423">
+        <f t="shared" si="71"/>
+        <v>71</v>
+      </c>
+      <c r="B423" t="s">
+        <v>20</v>
+      </c>
+      <c r="C423" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button71_Release = TimerIdOffsets.Button + 710 + TimerIdOffsets.Release,</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A424">
+        <f t="shared" si="71"/>
+        <v>71</v>
+      </c>
+      <c r="B424" t="s">
+        <v>21</v>
+      </c>
+      <c r="C424" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button71_Bomb = TimerIdOffsets.Button + 710 + TimerIdOffsets.Bomb,</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A425">
+        <f t="shared" si="71"/>
+        <v>71</v>
+      </c>
+      <c r="B425" t="s">
+        <v>22</v>
+      </c>
+      <c r="C425" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button71_LongBomb = TimerIdOffsets.Button + 710 + TimerIdOffsets.LongBomb,</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A426">
+        <f t="shared" si="71"/>
+        <v>71</v>
+      </c>
+      <c r="B426" t="s">
+        <v>23</v>
+      </c>
+      <c r="C426" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">        Play_Button71_Mine = TimerIdOffsets.Button + 710 + TimerIdOffsets.Mine,</v>
       </c>
     </row>
   </sheetData>
